--- a/data/Mörel-Filet/investment_decision/Mörel_SFH_from_2015_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Mörel_SFH_from_2015_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>277.7213407976261</v>
       </c>
       <c r="F2" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767951</v>
       </c>
       <c r="G2" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="H2" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767952</v>
       </c>
       <c r="I2" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="J2" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="K2" t="n">
         <v>277.7213407976261</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>277.7213407976261</v>
       </c>
       <c r="F3" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767951</v>
       </c>
       <c r="G3" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="H3" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767952</v>
       </c>
       <c r="I3" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="J3" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="K3" t="n">
         <v>277.7213407976261</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>277.7213407976261</v>
       </c>
       <c r="F4" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767951</v>
       </c>
       <c r="G4" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="H4" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767952</v>
       </c>
       <c r="I4" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="J4" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="K4" t="n">
         <v>277.7213407976261</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>277.7213407976261</v>
       </c>
       <c r="F5" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767951</v>
       </c>
       <c r="G5" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="H5" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767952</v>
       </c>
       <c r="I5" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="J5" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="K5" t="n">
         <v>277.7213407976261</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>277.7213407976261</v>
       </c>
       <c r="F6" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767951</v>
       </c>
       <c r="G6" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="H6" t="n">
-        <v>1.643181577979563</v>
+        <v>1.580267812767952</v>
       </c>
       <c r="I6" t="n">
         <v>277.7213407976261</v>
       </c>
       <c r="J6" t="n">
-        <v>1.694167905642874</v>
+        <v>1.58026781276795</v>
       </c>
       <c r="K6" t="n">
         <v>277.7213407976261</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4165820111964391</v>
+        <v>0.635112808988764</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001360228235294118</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0001363550333171104</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001363550333171104</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0001363550333171104</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001363550333171104</v>
+        <v>0.0001197000847058824</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.005780970000000015</v>
+        <v>0.01702811995567448</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.005780970000000017</v>
+        <v>0.01702811995567446</v>
       </c>
       <c r="G17" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.005780970000000017</v>
+        <v>0.01702811995567446</v>
       </c>
       <c r="I17" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.005780970000000015</v>
+        <v>0.01702811995567447</v>
       </c>
       <c r="K17" t="n">
         <v>0.09712029600000001</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06376715644971487</v>
+        <v>0.05158749173896281</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06376715644971487</v>
+        <v>0.05192790635278513</v>
       </c>
       <c r="G18" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06376715644971487</v>
+        <v>0.04950506148513762</v>
       </c>
       <c r="I18" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06376715644971487</v>
+        <v>0.04909449289917536</v>
       </c>
       <c r="K18" t="n">
         <v>0.09712029600000001</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06376715644971487</v>
+        <v>0.05158749173896281</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06376715644971488</v>
+        <v>0.05192790635278513</v>
       </c>
       <c r="G19" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.06376715644971488</v>
+        <v>0.04950506148513762</v>
       </c>
       <c r="I19" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06376715644971487</v>
+        <v>0.04909449289917536</v>
       </c>
       <c r="K19" t="n">
         <v>0.09712029600000001</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06359066999999999</v>
+        <v>0.04104315209608184</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06359066999999999</v>
+        <v>0.04104315209608185</v>
       </c>
       <c r="G20" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.06359066999999999</v>
+        <v>0.04100302733061825</v>
       </c>
       <c r="I20" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06359066999999999</v>
+        <v>0.04070355273175456</v>
       </c>
       <c r="K20" t="n">
         <v>0.09712029600000001</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.005604483550285123</v>
+        <v>0.006483780312793507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005604483550285123</v>
+        <v>0.006143365698971175</v>
       </c>
       <c r="G21" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.005604483550285123</v>
+        <v>0.008526085801155082</v>
       </c>
       <c r="I21" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.005604483550285123</v>
+        <v>0.008637179788253679</v>
       </c>
       <c r="K21" t="n">
         <v>0.09712029600000001</v>
@@ -1420,7 +1420,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.008671454999999996</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1434,19 +1434,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.008671454999999996</v>
       </c>
       <c r="G27" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.008671454999999996</v>
       </c>
       <c r="I27" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.008671454999999996</v>
       </c>
       <c r="K27" t="n">
         <v>0.09712029600000001</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.01484991116021255</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.01450949654639022</v>
       </c>
       <c r="G28" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.01693234141403774</v>
       </c>
       <c r="I28" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.01734291</v>
       </c>
       <c r="K28" t="n">
         <v>0.09712029600000001</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.01734291</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.01734291</v>
       </c>
       <c r="G29" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.01944131564486693</v>
       </c>
       <c r="I29" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.01944131564486695</v>
       </c>
       <c r="K29" t="n">
         <v>0.09712029600000001</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.02254751790391817</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.02254751790391815</v>
       </c>
       <c r="G30" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.0225876426693845</v>
       </c>
       <c r="I30" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.02288711726824543</v>
       </c>
       <c r="K30" t="n">
         <v>0.09712029600000001</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.020233395</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.09712029600000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.020233395</v>
       </c>
       <c r="G31" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.01979504826379083</v>
       </c>
       <c r="I31" t="n">
         <v>0.09712029600000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.02023653739241588</v>
       </c>
       <c r="K31" t="n">
         <v>0.09712029600000001</v>
@@ -2160,7 +2160,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0207403932094527</v>
+        <v>0.02777613742198145</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2174,19 +2174,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02458554808437867</v>
+        <v>0.03266126776194971</v>
       </c>
       <c r="G47" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H47" t="n">
-        <v>0.02458554808437867</v>
+        <v>0.0346593593313787</v>
       </c>
       <c r="I47" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0207403932094527</v>
+        <v>0.02841733306711983</v>
       </c>
       <c r="K47" t="n">
         <v>0.5265162753340651</v>
@@ -2197,7 +2197,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.0207403932094527</v>
+        <v>0.02777613742198145</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02458554808437867</v>
+        <v>0.03266126776194971</v>
       </c>
       <c r="G48" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H48" t="n">
-        <v>0.02458554808437867</v>
+        <v>0.0346593593313787</v>
       </c>
       <c r="I48" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0207403932094527</v>
+        <v>0.02841733306711983</v>
       </c>
       <c r="K48" t="n">
         <v>0.5265162753340651</v>
@@ -2234,7 +2234,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0207403932094527</v>
+        <v>0.02777613742198145</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2248,19 +2248,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F49" t="n">
-        <v>0.02458554808437867</v>
+        <v>0.03266126776194971</v>
       </c>
       <c r="G49" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H49" t="n">
-        <v>0.02458554808437867</v>
+        <v>0.0346593593313787</v>
       </c>
       <c r="I49" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0207403932094527</v>
+        <v>0.02841733306711983</v>
       </c>
       <c r="K49" t="n">
         <v>0.5265162753340651</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.03295902761311319</v>
+        <v>0.03653399000863686</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F52" t="n">
-        <v>0.01952505766685289</v>
+        <v>0.02529435329396396</v>
       </c>
       <c r="G52" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0190073541397957</v>
+        <v>0.02122417500173482</v>
       </c>
       <c r="I52" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J52" t="n">
-        <v>0.03225114163341061</v>
+        <v>0.03535324937030571</v>
       </c>
       <c r="K52" t="n">
         <v>0.5265162753340651</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.03295902761311319</v>
+        <v>0.03653399000863685</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F53" t="n">
-        <v>0.01952505766685289</v>
+        <v>0.02529435329396395</v>
       </c>
       <c r="G53" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0190073541397957</v>
+        <v>0.02122417500173482</v>
       </c>
       <c r="I53" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J53" t="n">
-        <v>0.03225114163341061</v>
+        <v>0.03535324937030571</v>
       </c>
       <c r="K53" t="n">
         <v>0.5265162753340651</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.03295902761311319</v>
+        <v>0.03653399000863686</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01952505766685289</v>
+        <v>0.02529435329396395</v>
       </c>
       <c r="G54" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0190073541397957</v>
+        <v>0.02122417500173482</v>
       </c>
       <c r="I54" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J54" t="n">
-        <v>0.03225114163341061</v>
+        <v>0.03535324937030571</v>
       </c>
       <c r="K54" t="n">
         <v>0.5265162753340651</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.134869228053767</v>
+        <v>0.1373183395173849</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1265467470948298</v>
+        <v>0.130908122276654</v>
       </c>
       <c r="G55" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1265467470948298</v>
+        <v>0.1308764158151272</v>
       </c>
       <c r="I55" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J55" t="n">
-        <v>0.134869228053767</v>
+        <v>0.1373183395173848</v>
       </c>
       <c r="K55" t="n">
         <v>0.5265162753340651</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.134869228053767</v>
+        <v>0.1373183395173849</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1265467470948298</v>
+        <v>0.130908122276654</v>
       </c>
       <c r="G56" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1265467470948298</v>
+        <v>0.1308764158151272</v>
       </c>
       <c r="I56" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J56" t="n">
-        <v>0.134869228053767</v>
+        <v>0.1373183395173849</v>
       </c>
       <c r="K56" t="n">
         <v>0.5265162753340651</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1111655684646381</v>
+        <v>0.04068685153408711</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1122902668689758</v>
+        <v>0.04172225271374356</v>
       </c>
       <c r="G62" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1122902668689758</v>
+        <v>0.04172225271374348</v>
       </c>
       <c r="I62" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J62" t="n">
-        <v>0.111165568464638</v>
+        <v>0.04068685153408707</v>
       </c>
       <c r="K62" t="n">
         <v>0.5265162753340651</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1111655684646381</v>
+        <v>0.04068685153408711</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1122902668689758</v>
+        <v>0.04172225271374356</v>
       </c>
       <c r="G63" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1122902668689758</v>
+        <v>0.04172225271374348</v>
       </c>
       <c r="I63" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J63" t="n">
-        <v>0.111165568464638</v>
+        <v>0.04068685153408707</v>
       </c>
       <c r="K63" t="n">
         <v>0.5265162753340651</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1111655684646381</v>
+        <v>0.04068685153408711</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1122902668689758</v>
+        <v>0.04172225271374356</v>
       </c>
       <c r="G64" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1122902668689758</v>
+        <v>0.04172225271374348</v>
       </c>
       <c r="I64" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J64" t="n">
-        <v>0.111165568464638</v>
+        <v>0.04068685153408707</v>
       </c>
       <c r="K64" t="n">
         <v>0.5265162753340651</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.06923454183476893</v>
+        <v>0.03177383217754998</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F65" t="n">
-        <v>0.07868172119804391</v>
+        <v>0.03818404941828083</v>
       </c>
       <c r="G65" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0786817211980439</v>
+        <v>0.03821575587980758</v>
       </c>
       <c r="I65" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J65" t="n">
-        <v>0.06923454183476893</v>
+        <v>0.03177383217754999</v>
       </c>
       <c r="K65" t="n">
         <v>0.5265162753340651</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.104060999189445</v>
+        <v>0.05667306560650728</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F66" t="n">
-        <v>0.11350817855272</v>
+        <v>0.06292062707031638</v>
       </c>
       <c r="G66" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1135081785527199</v>
+        <v>0.06298916456828306</v>
       </c>
       <c r="I66" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J66" t="n">
-        <v>0.104060999189445</v>
+        <v>0.05657118624186257</v>
       </c>
       <c r="K66" t="n">
         <v>0.5265162753340651</v>
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1161354874800185</v>
+        <v>0.1152207455427567</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,19 +3284,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1257243025513529</v>
+        <v>0.1205398507378049</v>
       </c>
       <c r="G77" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1262420060784101</v>
+        <v>0.122611937460605</v>
       </c>
       <c r="I77" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1168433734597211</v>
+        <v>0.1157602905359495</v>
       </c>
       <c r="K77" t="n">
         <v>0.5265162753340651</v>
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1161354874800185</v>
+        <v>0.1152207455427567</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,19 +3321,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1257243025513529</v>
+        <v>0.1205398507378049</v>
       </c>
       <c r="G78" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1262420060784101</v>
+        <v>0.122611937460605</v>
       </c>
       <c r="I78" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1168433734597211</v>
+        <v>0.1157602905359495</v>
       </c>
       <c r="K78" t="n">
         <v>0.5265162753340651</v>
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1161354874800185</v>
+        <v>0.1152207455427567</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,19 +3358,19 @@
         <v>0.5265162753340651</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1257243025513529</v>
+        <v>0.1205398507378049</v>
       </c>
       <c r="G79" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1262420060784101</v>
+        <v>0.122611937460605</v>
       </c>
       <c r="I79" t="n">
         <v>0.5265162753340651</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1168433734597211</v>
+        <v>0.1157602905359495</v>
       </c>
       <c r="K79" t="n">
         <v>0.5265162753340651</v>
